--- a/sensitivity_analysis/epsilon_c_sensitivity/model_sensitivity/graphs/SS_Comparison_epsilon_c_val.xlsx
+++ b/sensitivity_analysis/epsilon_c_sensitivity/model_sensitivity/graphs/SS_Comparison_epsilon_c_val.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="640" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="79" uniqueCount="79">
   <si>
     <t>Variable</t>
   </si>
@@ -181,9 +181,6 @@
   </si>
   <si>
     <t>xi</t>
-  </si>
-  <si>
-    <t>spread</t>
   </si>
   <si>
     <t>U_H</t>
@@ -298,13 +295,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E76"/>
+  <dimension ref="A1:E75"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.28515625" customWidth="true"/>
-    <col min="2" max="2" width="15.7109375" customWidth="true"/>
+    <col min="2" max="2" width="15.5703125" customWidth="true"/>
     <col min="3" max="3" width="15.7109375" customWidth="true"/>
-    <col min="4" max="4" width="15.7109375" customWidth="true"/>
+    <col min="4" max="4" width="14.7109375" customWidth="true"/>
     <col min="5" max="5" width="15.7109375" customWidth="true"/>
   </cols>
   <sheetData>
@@ -313,16 +310,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
+        <v>75</v>
+      </c>
+      <c r="C1" s="0" t="s">
         <v>76</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="D1" s="0" t="s">
         <v>77</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="E1" s="0" t="s">
         <v>78</v>
-      </c>
-      <c r="E1" s="0" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="2">
@@ -330,16 +327,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>0.14388215091402551</v>
+        <v>0.22044594474004953</v>
       </c>
       <c r="C2" s="0">
-        <v>0.14428960910359803</v>
+        <v>0.22098779215444392</v>
       </c>
       <c r="D2" s="0">
-        <v>0.14388214918743603</v>
+        <v>0.22044588383295993</v>
       </c>
       <c r="E2" s="0">
-        <v>0.14426146108859753</v>
+        <v>0.22091655467725141</v>
       </c>
     </row>
     <row r="3">
@@ -347,16 +344,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>0.32429476703190441</v>
+        <v>0.32141413782875433</v>
       </c>
       <c r="C3" s="0">
-        <v>0.32376524968509607</v>
+        <v>0.32069140954111869</v>
       </c>
       <c r="D3" s="0">
-        <v>0.32429476930289353</v>
+        <v>0.32141421923872082</v>
       </c>
       <c r="E3" s="0">
-        <v>0.32380156729276577</v>
+        <v>0.32078622865238754</v>
       </c>
     </row>
     <row r="4">
@@ -364,16 +361,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="0">
-        <v>0.046047592062484051</v>
+        <v>0.11337486336832386</v>
       </c>
       <c r="C4" s="0">
-        <v>0.018965932139719761</v>
+        <v>0.033807886794255192</v>
       </c>
       <c r="D4" s="0">
-        <v>0.04604770033190473</v>
+        <v>0.11338341989843458</v>
       </c>
       <c r="E4" s="0">
-        <v>0.020867396962384717</v>
+        <v>0.043929307169169263</v>
       </c>
     </row>
     <row r="5">
@@ -381,16 +378,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>7.2026023568761994e-07</v>
+        <v>3.0912574842893919e-05</v>
       </c>
       <c r="C5" s="0">
-        <v>0.029008268654093793</v>
+        <v>0.092170723816412919</v>
       </c>
       <c r="D5" s="0">
-        <v>6.0225333729317056e-07</v>
+        <v>2.0698456800562702e-05</v>
       </c>
       <c r="E5" s="0">
-        <v>0.026953272284354204</v>
+        <v>0.080186145438858616</v>
       </c>
     </row>
     <row r="6">
@@ -398,16 +395,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>0.046048300215381741</v>
+        <v>0.11340364667618352</v>
       </c>
       <c r="C6" s="0">
-        <v>0.047762013458020468</v>
+        <v>0.12313954699715227</v>
       </c>
       <c r="D6" s="0">
-        <v>0.046048296157328215</v>
+        <v>0.1134031549734848</v>
       </c>
       <c r="E6" s="0">
-        <v>0.047691095510123786</v>
+        <v>0.1223138572731487</v>
       </c>
     </row>
     <row r="7">
@@ -415,16 +412,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>0.40603757054046391</v>
+        <v>0.38778758045286177</v>
       </c>
       <c r="C7" s="0">
-        <v>0.40558179556450591</v>
+        <v>0.38760108113848307</v>
       </c>
       <c r="D7" s="0">
-        <v>0.40603757243356303</v>
+        <v>0.38778760149858016</v>
       </c>
       <c r="E7" s="0">
-        <v>0.40561357771390472</v>
+        <v>0.38762558169200284</v>
       </c>
     </row>
     <row r="8">
@@ -432,16 +429,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="0">
-        <v>0.33210481279842757</v>
+        <v>0.32060759189760435</v>
       </c>
       <c r="C8" s="0">
-        <v>0.33254650563002836</v>
+        <v>0.32059184182600731</v>
       </c>
       <c r="D8" s="0">
-        <v>0.33210481097386191</v>
+        <v>0.32060759361784175</v>
       </c>
       <c r="E8" s="0">
-        <v>0.33251560451629864</v>
+        <v>0.32059389751254824</v>
       </c>
     </row>
     <row r="9">
@@ -449,16 +446,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="0">
-        <v>1.621158881425006</v>
+        <v>1.6725579771688905</v>
       </c>
       <c r="C9" s="0">
-        <v>1.6202330166730439</v>
+        <v>1.6803615600989337</v>
       </c>
       <c r="D9" s="0">
-        <v>1.6211588852162218</v>
+        <v>1.6725571088644096</v>
       </c>
       <c r="E9" s="0">
-        <v>1.6202981954584197</v>
+        <v>1.6793352051046955</v>
       </c>
     </row>
     <row r="10">
@@ -466,16 +463,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="0">
-        <v>0.86236991728186274</v>
+        <v>3.764021575452098</v>
       </c>
       <c r="C10" s="0">
-        <v>0.85022243459771296</v>
+        <v>3.7525626470097779</v>
       </c>
       <c r="D10" s="0">
-        <v>0.8623699674916343</v>
+        <v>3.7640228589112126</v>
       </c>
       <c r="E10" s="0">
-        <v>0.85107167827934005</v>
+        <v>3.7540651116881625</v>
       </c>
     </row>
     <row r="11">
@@ -483,16 +480,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="0">
-        <v>11.621460862346376</v>
+        <v>0.46701336213906386</v>
       </c>
       <c r="C11" s="0">
-        <v>11.671597051845797</v>
+        <v>0.46023917018812383</v>
       </c>
       <c r="D11" s="0">
-        <v>11.621460655034504</v>
+        <v>0.46701412001014686</v>
       </c>
       <c r="E11" s="0">
-        <v>11.668112344365811</v>
+        <v>0.46112626550030611</v>
       </c>
     </row>
     <row r="12">
@@ -500,16 +497,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="0">
-        <v>4.3516259959246586</v>
+        <v>3.3097680913244374</v>
       </c>
       <c r="C12" s="0">
-        <v>4.4062520162904226</v>
+        <v>3.2785537596042653</v>
       </c>
       <c r="D12" s="0">
-        <v>4.3516257722429197</v>
+        <v>3.3097715645423618</v>
       </c>
       <c r="E12" s="0">
-        <v>4.4024064679532477</v>
+        <v>3.282659179581219</v>
       </c>
     </row>
     <row r="13">
@@ -517,16 +514,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="0">
-        <v>49.03789262672111</v>
+        <v>14.489057422092559</v>
       </c>
       <c r="C13" s="0">
-        <v>48.244155609512525</v>
+        <v>14.380357534985771</v>
       </c>
       <c r="D13" s="0">
-        <v>49.037895978596737</v>
+        <v>14.489070843868674</v>
       </c>
       <c r="E13" s="0">
-        <v>48.300402248611498</v>
+        <v>14.395683183712512</v>
       </c>
     </row>
     <row r="14">
@@ -534,16 +531,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="0">
-        <v>402.69829513562496</v>
+        <v>32.766084020211444</v>
       </c>
       <c r="C14" s="0">
-        <v>403.09051505301409</v>
+        <v>32.739232580655198</v>
       </c>
       <c r="D14" s="0">
-        <v>402.69829352711548</v>
+        <v>32.766087039212621</v>
       </c>
       <c r="E14" s="0">
-        <v>403.06297854366818</v>
+        <v>32.742756736309907</v>
       </c>
     </row>
     <row r="15">
@@ -551,16 +548,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="0">
-        <v>10.067457378390623</v>
+        <v>0.81915210050528586</v>
       </c>
       <c r="C15" s="0">
-        <v>10.077262876325353</v>
+        <v>0.81848081451638011</v>
       </c>
       <c r="D15" s="0">
-        <v>10.067457338177888</v>
+        <v>0.81915217598031531</v>
       </c>
       <c r="E15" s="0">
-        <v>10.076574463591703</v>
+        <v>0.81856891840774793</v>
       </c>
     </row>
     <row r="16">
@@ -568,16 +565,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="0">
-        <v>9.3605834813915028</v>
+        <v>0.77403060902948795</v>
       </c>
       <c r="C16" s="0">
-        <v>9.4212947302050889</v>
+        <v>0.76886942746758069</v>
       </c>
       <c r="D16" s="0">
-        <v>9.3605832288444422</v>
+        <v>0.77403117588665438</v>
       </c>
       <c r="E16" s="0">
-        <v>9.417069653174476</v>
+        <v>0.76953609627038666</v>
       </c>
     </row>
     <row r="17">
@@ -585,16 +582,16 @@
         <v>16</v>
       </c>
       <c r="B17" s="0">
-        <v>0.41332963560794767</v>
+        <v>0.31203934076507589</v>
       </c>
       <c r="C17" s="0">
-        <v>0.41372507354295562</v>
+        <v>0.31155824555142753</v>
       </c>
       <c r="D17" s="0">
-        <v>0.41332963396112166</v>
+        <v>0.31203939451692669</v>
       </c>
       <c r="E17" s="0">
-        <v>0.41369771873030087</v>
+        <v>0.31162113656545748</v>
       </c>
     </row>
     <row r="18">
@@ -619,16 +616,16 @@
         <v>18</v>
       </c>
       <c r="B19" s="0">
-        <v>0.093605834813915031</v>
+        <v>0.077403060902948809</v>
       </c>
       <c r="C19" s="0">
-        <v>0.094212947302050903</v>
+        <v>0.076886942746758072</v>
       </c>
       <c r="D19" s="0">
-        <v>0.093605832288444421</v>
+        <v>0.077403117588665443</v>
       </c>
       <c r="E19" s="0">
-        <v>0.094170696531744758</v>
+        <v>0.076953609627038663</v>
       </c>
     </row>
     <row r="20">
@@ -636,16 +633,16 @@
         <v>19</v>
       </c>
       <c r="B20" s="0">
-        <v>0.018419036824993622</v>
+        <v>0.056687431684161932</v>
       </c>
       <c r="C20" s="0">
-        <v>0.007586372855887904</v>
+        <v>0.016903943397127596</v>
       </c>
       <c r="D20" s="0">
-        <v>0.018419080132761896</v>
+        <v>0.056691709949217288</v>
       </c>
       <c r="E20" s="0">
-        <v>0.0083469587849538882</v>
+        <v>0.021964653584584631</v>
       </c>
     </row>
     <row r="21">
@@ -653,16 +650,16 @@
         <v>20</v>
       </c>
       <c r="B21" s="0">
-        <v>0.50879825119629896</v>
+        <v>1.5056086301808393</v>
       </c>
       <c r="C21" s="0">
-        <v>0.50163123641265062</v>
+        <v>1.5010250588039113</v>
       </c>
       <c r="D21" s="0">
-        <v>0.50879828082006417</v>
+        <v>1.5056091435644852</v>
       </c>
       <c r="E21" s="0">
-        <v>0.50213229018481054</v>
+        <v>1.5016260446752652</v>
       </c>
     </row>
     <row r="22">
@@ -670,16 +667,16 @@
         <v>21</v>
       </c>
       <c r="B22" s="0">
-        <v>0.49037892626721108</v>
+        <v>1.4489057422092559</v>
       </c>
       <c r="C22" s="0">
-        <v>0.48244155609512523</v>
+        <v>1.4380357534985773</v>
       </c>
       <c r="D22" s="0">
-        <v>0.49037895978596735</v>
+        <v>1.4489070843868677</v>
       </c>
       <c r="E22" s="0">
-        <v>0.48300402248611501</v>
+        <v>1.4395683183712511</v>
       </c>
     </row>
     <row r="23">
@@ -687,16 +684,16 @@
         <v>22</v>
       </c>
       <c r="B23" s="0">
-        <v>0.51400425182600518</v>
+        <v>0.39396171402600266</v>
       </c>
       <c r="C23" s="0">
-        <v>0.51450488147262663</v>
+        <v>0.39363886680553178</v>
       </c>
       <c r="D23" s="0">
-        <v>0.51400424977290315</v>
+        <v>0.39396175032484398</v>
       </c>
       <c r="E23" s="0">
-        <v>0.51446973386198336</v>
+        <v>0.39368123935152682</v>
       </c>
     </row>
     <row r="24">
@@ -704,16 +701,16 @@
         <v>23</v>
       </c>
       <c r="B24" s="0">
-        <v>4.0269829513562492</v>
+        <v>3.2766084020211443</v>
       </c>
       <c r="C24" s="0">
-        <v>4.030905150530141</v>
+        <v>3.27392325806552</v>
       </c>
       <c r="D24" s="0">
-        <v>4.026982935271155</v>
+        <v>3.2766087039212621</v>
       </c>
       <c r="E24" s="0">
-        <v>4.0306297854366813</v>
+        <v>3.2742756736309908</v>
       </c>
     </row>
     <row r="25">
@@ -721,16 +718,16 @@
         <v>24</v>
       </c>
       <c r="B25" s="0">
-        <v>0.10067457378390623</v>
+        <v>0.081915210050528597</v>
       </c>
       <c r="C25" s="0">
-        <v>0.10077262876325353</v>
+        <v>0.081848081451638022</v>
       </c>
       <c r="D25" s="0">
-        <v>0.10067457338177889</v>
+        <v>0.081915217598031539</v>
       </c>
       <c r="E25" s="0">
-        <v>0.10076574463591703</v>
+        <v>0.081856891840774798</v>
       </c>
     </row>
     <row r="26">
@@ -738,16 +735,16 @@
         <v>25</v>
       </c>
       <c r="B26" s="0">
-        <v>0.18647984997921976</v>
+        <v>0.1387823409522691</v>
       </c>
       <c r="C26" s="0">
-        <v>0.18666147754565615</v>
+        <v>0.13866861037533307</v>
       </c>
       <c r="D26" s="0">
-        <v>0.18647984923435784</v>
+        <v>0.13878235373939538</v>
       </c>
       <c r="E26" s="0">
-        <v>0.18664872605354957</v>
+        <v>0.13868353710784526</v>
       </c>
     </row>
     <row r="27">
@@ -755,16 +752,16 @@
         <v>26</v>
       </c>
       <c r="B27" s="0">
-        <v>0.83333333333333326</v>
+        <v>0.83333333333333315</v>
       </c>
       <c r="C27" s="0">
-        <v>0.83333333333333348</v>
+        <v>0.83333333333333293</v>
       </c>
       <c r="D27" s="0">
-        <v>0.83333333333333337</v>
+        <v>0.83333333333333282</v>
       </c>
       <c r="E27" s="0">
-        <v>0.83333333333333337</v>
+        <v>0.83333333333333293</v>
       </c>
     </row>
     <row r="28">
@@ -772,16 +769,16 @@
         <v>27</v>
       </c>
       <c r="B28" s="0">
-        <v>0.085667375304334131</v>
+        <v>0.06566028567100049</v>
       </c>
       <c r="C28" s="0">
-        <v>0.085750813578770971</v>
+        <v>0.065606477800922144</v>
       </c>
       <c r="D28" s="0">
-        <v>0.085667374962150517</v>
+        <v>0.065660291720807548</v>
       </c>
       <c r="E28" s="0">
-        <v>0.085744955643663995</v>
+        <v>0.065613539891921327</v>
       </c>
     </row>
     <row r="29">
@@ -806,16 +803,16 @@
         <v>29</v>
       </c>
       <c r="B30" s="0">
-        <v>0.0079384595095809089</v>
+        <v>0.01174277523194831</v>
       </c>
       <c r="C30" s="0">
-        <v>0.0084621337232799361</v>
+        <v>0.011280464945835929</v>
       </c>
       <c r="D30" s="0">
-        <v>0.0079384573262939202</v>
+        <v>0.011742825867857911</v>
       </c>
       <c r="E30" s="0">
-        <v>0.0084257408880807697</v>
+        <v>0.011340069735117343</v>
       </c>
     </row>
     <row r="31">
@@ -840,16 +837,16 @@
         <v>31</v>
       </c>
       <c r="B32" s="0">
-        <v>0.041987222448680792</v>
+        <v>4.0182675188718049</v>
       </c>
       <c r="C32" s="0">
-        <v>0.04175760593837876</v>
+        <v>4.1039437027936936</v>
       </c>
       <c r="D32" s="0">
-        <v>0.041987223404466881</v>
+        <v>4.0182581078358357</v>
       </c>
       <c r="E32" s="0">
-        <v>0.041773459952105685</v>
+        <v>4.0925473962187588</v>
       </c>
     </row>
     <row r="33">
@@ -857,16 +854,16 @@
         <v>32</v>
       </c>
       <c r="B33" s="0">
-        <v>0.05038466693841695</v>
+        <v>4.8219210226461664</v>
       </c>
       <c r="C33" s="0">
-        <v>0.050109127126054503</v>
+        <v>4.9247324433524327</v>
       </c>
       <c r="D33" s="0">
-        <v>0.050384668085360268</v>
+        <v>4.8219097294030036</v>
       </c>
       <c r="E33" s="0">
-        <v>0.050128151942526823</v>
+        <v>4.9110568754625108</v>
       </c>
     </row>
     <row r="34">
@@ -874,16 +871,16 @@
         <v>33</v>
       </c>
       <c r="B34" s="0">
-        <v>0.05755286036561022</v>
+        <v>0.066133783422014883</v>
       </c>
       <c r="C34" s="0">
-        <v>0.057715843641439217</v>
+        <v>0.066296337646333178</v>
       </c>
       <c r="D34" s="0">
-        <v>0.057552859674974428</v>
+        <v>0.066133765149887974</v>
       </c>
       <c r="E34" s="0">
-        <v>0.057704584435439035</v>
+        <v>0.066274966403175442</v>
       </c>
     </row>
     <row r="35">
@@ -891,16 +888,16 @@
         <v>34</v>
       </c>
       <c r="B35" s="0">
-        <v>0</v>
+        <v>0.089359545030377144</v>
       </c>
       <c r="C35" s="0">
-        <v>0</v>
+        <v>0.089286315882192158</v>
       </c>
       <c r="D35" s="0">
-        <v>0</v>
+        <v>0.089359553263786168</v>
       </c>
       <c r="E35" s="0">
-        <v>0</v>
+        <v>0.089295926946661372</v>
       </c>
     </row>
     <row r="36">
@@ -908,16 +905,16 @@
         <v>35</v>
       </c>
       <c r="B36" s="0">
-        <v>-2.3021144146244086</v>
+        <v>-0.68810709723158303</v>
       </c>
       <c r="C36" s="0">
-        <v>-2.308633745657569</v>
+        <v>-0.68862695176043454</v>
       </c>
       <c r="D36" s="0">
-        <v>-2.3021143869989773</v>
+        <v>-0.68810703880458457</v>
       </c>
       <c r="E36" s="0">
-        <v>-2.3081833774175613</v>
+        <v>-0.68855853980252257</v>
       </c>
     </row>
     <row r="37">
@@ -942,16 +939,16 @@
         <v>37</v>
       </c>
       <c r="B38" s="0">
-        <v>0.00092123994534395613</v>
+        <v>0.0014326420795254954</v>
       </c>
       <c r="C38" s="0">
-        <v>0.011982626104431912</v>
+        <v>0.046507960493134645</v>
       </c>
       <c r="D38" s="0">
-        <v>0.00092119490797301195</v>
+        <v>0.0014276419771307135</v>
       </c>
       <c r="E38" s="0">
-        <v>0.011198656852989377</v>
+        <v>0.040642189059043925</v>
       </c>
     </row>
     <row r="39">
@@ -959,16 +956,16 @@
         <v>38</v>
       </c>
       <c r="B39" s="0">
-        <v>0.00092095184124968118</v>
+        <v>0.0014171857921040484</v>
       </c>
       <c r="C39" s="0">
-        <v>0.00037931864279439526</v>
+        <v>0.00042259858492818992</v>
       </c>
       <c r="D39" s="0">
-        <v>0.00092095400663809478</v>
+        <v>0.0014172927487304322</v>
       </c>
       <c r="E39" s="0">
-        <v>0.00041734793924769442</v>
+        <v>0.00054911633961461572</v>
       </c>
     </row>
     <row r="40">
@@ -993,16 +990,16 @@
         <v>40</v>
       </c>
       <c r="B41" s="0">
-        <v>1.5389636322717954</v>
+        <v>1.5849419709205088</v>
       </c>
       <c r="C41" s="0">
-        <v>1.5389636322717959</v>
+        <v>1.5849419709205081</v>
       </c>
       <c r="D41" s="0">
-        <v>1.5389636322717959</v>
+        <v>1.5849419709205077</v>
       </c>
       <c r="E41" s="0">
-        <v>1.5389636322717957</v>
+        <v>1.5849419709205081</v>
       </c>
     </row>
     <row r="42">
@@ -1010,16 +1007,16 @@
         <v>41</v>
       </c>
       <c r="B42" s="0">
-        <v>0.26548597428414716</v>
+        <v>0.47904977341267413</v>
       </c>
       <c r="C42" s="0">
-        <v>0.2661791768273557</v>
+        <v>0.47973592639510576</v>
       </c>
       <c r="D42" s="0">
-        <v>0.26548597136454916</v>
+        <v>0.47904969621438159</v>
       </c>
       <c r="E42" s="0">
-        <v>0.26613114056915171</v>
+        <v>0.47964574942300497</v>
       </c>
     </row>
     <row r="43">
@@ -1027,16 +1024,16 @@
         <v>42</v>
       </c>
       <c r="B43" s="0">
-        <v>1.2888897183752741</v>
+        <v>1.1148774675169169</v>
       </c>
       <c r="C43" s="0">
-        <v>1.2884314822599963</v>
+        <v>1.1140185648348173</v>
       </c>
       <c r="D43" s="0">
-        <v>1.2888897203081142</v>
+        <v>1.1148775642575519</v>
       </c>
       <c r="E43" s="0">
-        <v>1.2884631925000705</v>
+        <v>1.1141313373647601</v>
       </c>
     </row>
     <row r="44">
@@ -1044,16 +1041,16 @@
         <v>43</v>
       </c>
       <c r="B44" s="0">
-        <v>2.1820903494289521</v>
+        <v>3.3126658405253546</v>
       </c>
       <c r="C44" s="0">
-        <v>2.1555022571662303</v>
+        <v>3.2872438346220321</v>
       </c>
       <c r="D44" s="0">
-        <v>2.1820904593225521</v>
+        <v>3.3126686898448012</v>
       </c>
       <c r="E44" s="0">
-        <v>2.1573613445824797</v>
+        <v>3.2905698539826873</v>
       </c>
     </row>
     <row r="45">
@@ -1078,16 +1075,16 @@
         <v>45</v>
       </c>
       <c r="B46" s="0">
-        <v>0.035101010101010167</v>
+        <v>0.033064516129032252</v>
       </c>
       <c r="C46" s="0">
-        <v>0.035101010101010167</v>
+        <v>0.033064516129032252</v>
       </c>
       <c r="D46" s="0">
-        <v>0.035101010101010167</v>
+        <v>0.033064516129032252</v>
       </c>
       <c r="E46" s="0">
-        <v>0.035101010101010167</v>
+        <v>0.033064516129032252</v>
       </c>
     </row>
     <row r="47">
@@ -1095,16 +1092,16 @@
         <v>46</v>
       </c>
       <c r="B47" s="0">
-        <v>0.0050723844992070014</v>
+        <v>0.002986042183622827</v>
       </c>
       <c r="C47" s="0">
-        <v>0.0053350924204853415</v>
+        <v>0.002986042183622827</v>
       </c>
       <c r="D47" s="0">
-        <v>0.0050723834295694414</v>
+        <v>0.002986042183622827</v>
       </c>
       <c r="E47" s="0">
-        <v>0.0053164731507635808</v>
+        <v>0.002986042183622827</v>
       </c>
     </row>
     <row r="48">
@@ -1112,16 +1109,16 @@
         <v>47</v>
       </c>
       <c r="B48" s="0">
-        <v>0.025521423762333982</v>
+        <v>0.015677419354838702</v>
       </c>
       <c r="C48" s="0">
-        <v>0.026912476870219283</v>
+        <v>0.015677419354838702</v>
       </c>
       <c r="D48" s="0">
-        <v>0.025521418098543389</v>
+        <v>0.015677419354838702</v>
       </c>
       <c r="E48" s="0">
-        <v>0.026813886797689389</v>
+        <v>0.015677419354838702</v>
       </c>
     </row>
     <row r="49">
@@ -1129,16 +1126,16 @@
         <v>48</v>
       </c>
       <c r="B49" s="0">
-        <v>0.010101010101010166</v>
+        <v>0.0080645161290322509</v>
       </c>
       <c r="C49" s="0">
-        <v>0.010101010101010166</v>
+        <v>0.0080645161290322509</v>
       </c>
       <c r="D49" s="0">
-        <v>0.010101010101010166</v>
+        <v>0.0080645161290322509</v>
       </c>
       <c r="E49" s="0">
-        <v>0.010101010101010166</v>
+        <v>0.0080645161290322509</v>
       </c>
     </row>
     <row r="50">
@@ -1146,16 +1143,16 @@
         <v>49</v>
       </c>
       <c r="B50" s="0">
-        <v>0.010147072098277364</v>
+        <v>0.013064516129032252</v>
       </c>
       <c r="C50" s="0">
-        <v>0.010700141406231762</v>
+        <v>0.013064516129032252</v>
       </c>
       <c r="D50" s="0">
-        <v>0.010147069846408816</v>
+        <v>0.013064516129032252</v>
       </c>
       <c r="E50" s="0">
-        <v>0.010660942943659634</v>
+        <v>0.013064516129032252</v>
       </c>
     </row>
     <row r="51">
@@ -1214,16 +1211,16 @@
         <v>53</v>
       </c>
       <c r="B54" s="0">
-        <v>0.02026896088947865</v>
+        <v>0.019198383854861931</v>
       </c>
       <c r="C54" s="0">
-        <v>0.015079201532185754</v>
+        <v>0.019212241850615264</v>
       </c>
       <c r="D54" s="0">
-        <v>0.02026898198161738</v>
+        <v>0.019198382291980547</v>
       </c>
       <c r="E54" s="0">
-        <v>0.015447629066027093</v>
+        <v>0.019210420364325315</v>
       </c>
     </row>
     <row r="55">
@@ -1265,16 +1262,16 @@
         <v>56</v>
       </c>
       <c r="B57" s="0">
-        <v>0.0050286256018031647</v>
+        <v>-4.9389319817457409</v>
       </c>
       <c r="C57" s="0">
-        <v>0.0047659176805248246</v>
+        <v>-4.9285259605580558</v>
       </c>
       <c r="D57" s="0">
-        <v>0.0050286266714407247</v>
+        <v>-4.9389330129534086</v>
       </c>
       <c r="E57" s="0">
-        <v>0.0047845369502465852</v>
+        <v>-4.9297688557906607</v>
       </c>
     </row>
     <row r="58">
@@ -1282,16 +1279,16 @@
         <v>57</v>
       </c>
       <c r="B58" s="0">
-        <v>-5.9968248937316</v>
+        <v>-164.63106605819189</v>
       </c>
       <c r="C58" s="0">
-        <v>-5.9856287006100573</v>
+        <v>-164.28419868526814</v>
       </c>
       <c r="D58" s="0">
-        <v>-5.9968249383117715</v>
+        <v>-164.63110043177986</v>
       </c>
       <c r="E58" s="0">
-        <v>-5.9863514657541277</v>
+        <v>-164.32562852635465</v>
       </c>
     </row>
     <row r="59">
@@ -1299,16 +1296,16 @@
         <v>58</v>
       </c>
       <c r="B59" s="0">
-        <v>-99.947081562193162</v>
+        <v>0.22044594474004836</v>
       </c>
       <c r="C59" s="0">
-        <v>-99.760478343500793</v>
+        <v>0.22098779215444281</v>
       </c>
       <c r="D59" s="0">
-        <v>-99.947082305196233</v>
+        <v>0.22044588383295868</v>
       </c>
       <c r="E59" s="0">
-        <v>-99.772524429235261</v>
+        <v>0.22091655467725035</v>
       </c>
     </row>
     <row r="60">
@@ -1316,16 +1313,16 @@
         <v>59</v>
       </c>
       <c r="B60" s="0">
-        <v>0.14388215091388537</v>
+        <v>0.11340577594316675</v>
       </c>
       <c r="C60" s="0">
-        <v>0.14428960910341526</v>
+        <v>0.12597861061066812</v>
       </c>
       <c r="D60" s="0">
-        <v>0.14388214918729586</v>
+        <v>0.11340411835523515</v>
       </c>
       <c r="E60" s="0">
-        <v>0.14426146108841811</v>
+        <v>0.12411545260802788</v>
       </c>
     </row>
     <row r="61">
@@ -1333,16 +1330,16 @@
         <v>60</v>
       </c>
       <c r="B61" s="0">
-        <v>0.046048312322719741</v>
+        <v>-4.601652410435638</v>
       </c>
       <c r="C61" s="0">
-        <v>0.047974200793813551</v>
+        <v>-4.6005668674852309</v>
       </c>
       <c r="D61" s="0">
-        <v>0.046048302585242021</v>
+        <v>-4.6016525306134515</v>
       </c>
       <c r="E61" s="0">
-        <v>0.047820669246738917</v>
+        <v>-4.6007089513992456</v>
       </c>
     </row>
     <row r="62">
@@ -1350,16 +1347,16 @@
         <v>61</v>
       </c>
       <c r="B62" s="0">
-        <v>-4.585833854849632</v>
+        <v>-230.08262052178191</v>
       </c>
       <c r="C62" s="0">
-        <v>-4.5895827148680395</v>
+        <v>-230.02834337426231</v>
       </c>
       <c r="D62" s="0">
-        <v>-4.5858338393430662</v>
+        <v>-230.08262653067271</v>
       </c>
       <c r="E62" s="0">
-        <v>-4.5893205682322264</v>
+        <v>-230.03544756996229</v>
       </c>
     </row>
     <row r="63">
@@ -1367,16 +1364,16 @@
         <v>62</v>
       </c>
       <c r="B63" s="0">
-        <v>-152.86112849498761</v>
+        <v>0.44679772515187544</v>
       </c>
       <c r="C63" s="0">
-        <v>-152.98609049560156</v>
+        <v>0.44643157941095157</v>
       </c>
       <c r="D63" s="0">
-        <v>-152.86112797810188</v>
+        <v>0.44679776631892065</v>
       </c>
       <c r="E63" s="0">
-        <v>-152.97735227440808</v>
+        <v>0.4464796347332976</v>
       </c>
     </row>
     <row r="64">
@@ -1384,16 +1381,16 @@
         <v>63</v>
       </c>
       <c r="B64" s="0">
-        <v>0.42804647863883843</v>
+        <v>1.7766041018134713</v>
       </c>
       <c r="C64" s="0">
-        <v>0.42846338716927962</v>
+        <v>1.7711955313613008</v>
       </c>
       <c r="D64" s="0">
-        <v>0.42804647692907999</v>
+        <v>1.7766047076012597</v>
       </c>
       <c r="E64" s="0">
-        <v>0.42843411735116099</v>
+        <v>1.7719046889611816</v>
       </c>
     </row>
     <row r="65">
@@ -1401,16 +1398,16 @@
         <v>64</v>
       </c>
       <c r="B65" s="0">
-        <v>2.6751452327666776</v>
+        <v>-3.4762822685648609</v>
       </c>
       <c r="C65" s="0">
-        <v>2.6421934899762838</v>
+        <v>-3.5003522205237143</v>
       </c>
       <c r="D65" s="0">
-        <v>2.6751453689846674</v>
+        <v>-3.4762796055013778</v>
       </c>
       <c r="E65" s="0">
-        <v>2.6444970152994021</v>
+        <v>-3.4971697071883234</v>
       </c>
     </row>
     <row r="66">
@@ -1418,16 +1415,16 @@
         <v>65</v>
       </c>
       <c r="B66" s="0">
-        <v>-0.59147150871334331</v>
+        <v>-434.53528357061282</v>
       </c>
       <c r="C66" s="0">
-        <v>-0.59018028664177979</v>
+        <v>-437.54402756546733</v>
       </c>
       <c r="D66" s="0">
-        <v>-0.59147151406933429</v>
+        <v>-434.53495068767205</v>
       </c>
       <c r="E66" s="0">
-        <v>-0.59026977827592308</v>
+        <v>-437.14621339854369</v>
       </c>
     </row>
     <row r="67">
@@ -1435,16 +1432,16 @@
         <v>66</v>
       </c>
       <c r="B67" s="0">
-        <v>-59.147150871335008</v>
+        <v>1.2861654626443519</v>
       </c>
       <c r="C67" s="0">
-        <v>-59.018028664177812</v>
+        <v>1.2787199847045017</v>
       </c>
       <c r="D67" s="0">
-        <v>-59.147151406933595</v>
+        <v>1.2861662959904601</v>
       </c>
       <c r="E67" s="0">
-        <v>-59.026977827592042</v>
+        <v>1.2796951839080504</v>
       </c>
     </row>
     <row r="68">
@@ -1452,16 +1449,16 @@
         <v>67</v>
       </c>
       <c r="B68" s="0">
-        <v>21.688918240736999</v>
+        <v>58.219297138495271</v>
       </c>
       <c r="C68" s="0">
-        <v>21.748859928171154</v>
+        <v>57.896995748376973</v>
       </c>
       <c r="D68" s="0">
-        <v>21.688917993212396</v>
+        <v>58.219334515479417</v>
       </c>
       <c r="E68" s="0">
-        <v>21.744686807957535</v>
+        <v>57.940259257251917</v>
       </c>
     </row>
     <row r="69">
@@ -1469,16 +1466,16 @@
         <v>68</v>
       </c>
       <c r="B69" s="0">
-        <v>461.23182885237742</v>
+        <v>-217.80210959487002</v>
       </c>
       <c r="C69" s="0">
-        <v>460.83235682928387</v>
+        <v>-217.90783944888574</v>
       </c>
       <c r="D69" s="0">
-        <v>461.23183058586562</v>
+        <v>-217.80209589692623</v>
       </c>
       <c r="E69" s="0">
-        <v>460.86096232938189</v>
+        <v>-217.89161463101664</v>
       </c>
     </row>
     <row r="70">
@@ -1486,16 +1483,16 @@
         <v>69</v>
       </c>
       <c r="B70" s="0">
-        <v>-130.75836994563329</v>
+        <v>41.755860869520959</v>
       </c>
       <c r="C70" s="0">
-        <v>-130.75616501644703</v>
+        <v>41.693852631205218</v>
       </c>
       <c r="D70" s="0">
-        <v>-130.75836994322793</v>
+        <v>41.755867804309368</v>
       </c>
       <c r="E70" s="0">
-        <v>-130.75591739187078</v>
+        <v>41.701964962274928</v>
       </c>
     </row>
     <row r="71">
@@ -1503,16 +1500,16 @@
         <v>70</v>
       </c>
       <c r="B71" s="0">
-        <v>52.698946516983881</v>
+        <v>658.92742425464996</v>
       </c>
       <c r="C71" s="0">
-        <v>52.799784135295269</v>
+        <v>656.11670926875524</v>
       </c>
       <c r="D71" s="0">
-        <v>52.698946099519951</v>
+        <v>658.92773937660638</v>
       </c>
       <c r="E71" s="0">
-        <v>52.792758175212761</v>
+        <v>656.48455276136792</v>
       </c>
     </row>
     <row r="72">
@@ -1520,16 +1517,16 @@
         <v>71</v>
       </c>
       <c r="B72" s="0">
-        <v>620.90733007852009</v>
+        <v>0.88354642704923714</v>
       </c>
       <c r="C72" s="0">
-        <v>618.6407407696372</v>
+        <v>0.88241916309224033</v>
       </c>
       <c r="D72" s="0">
-        <v>620.90733945937075</v>
+        <v>0.88354657174638218</v>
       </c>
       <c r="E72" s="0">
-        <v>618.79911300191611</v>
+        <v>0.88258374113355875</v>
       </c>
     </row>
     <row r="73">
@@ -1537,16 +1534,16 @@
         <v>72</v>
       </c>
       <c r="B73" s="0">
-        <v>0.74283521309701706</v>
+        <v>0.83402841534261063</v>
       </c>
       <c r="C73" s="0">
-        <v>0.74491110342324462</v>
+        <v>0.83256929332087692</v>
       </c>
       <c r="D73" s="0">
-        <v>0.74283520466590736</v>
+        <v>0.83402860459628281</v>
       </c>
       <c r="E73" s="0">
-        <v>0.74476668218487707</v>
+        <v>0.8327841374542968</v>
       </c>
     </row>
     <row r="74">
@@ -1554,16 +1551,16 @@
         <v>73</v>
       </c>
       <c r="B74" s="0">
-        <v>0.8327642754816259</v>
+        <v>0.3164371149960572</v>
       </c>
       <c r="C74" s="0">
-        <v>0.83387577094342669</v>
+        <v>0.31483514956423503</v>
       </c>
       <c r="D74" s="0">
-        <v>0.83276427108836426</v>
+        <v>0.3164372943011679</v>
       </c>
       <c r="E74" s="0">
-        <v>0.83379972938747227</v>
+        <v>0.31504551298383837</v>
       </c>
     </row>
     <row r="75">
@@ -1571,32 +1568,15 @@
         <v>74</v>
       </c>
       <c r="B75" s="0">
-        <v>0.5288190514566482</v>
+        <v>0</v>
       </c>
       <c r="C75" s="0">
-        <v>0.52892949671178469</v>
+        <v>0</v>
       </c>
       <c r="D75" s="0">
-        <v>0.52881905103557969</v>
+        <v>0</v>
       </c>
       <c r="E75" s="0">
-        <v>0.52892167181968996</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="0" t="s">
-        <v>75</v>
-      </c>
-      <c r="B76" s="0">
-        <v>0</v>
-      </c>
-      <c r="C76" s="0">
-        <v>0</v>
-      </c>
-      <c r="D76" s="0">
-        <v>0</v>
-      </c>
-      <c r="E76" s="0">
         <v>0</v>
       </c>
     </row>
